--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -268,7 +268,7 @@
     <t>患者への注射薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な受療行動と結びつけます。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
